--- a/manuscript/post-feedback-from-atanu/Supplementary-Table-3.xlsx
+++ b/manuscript/post-feedback-from-atanu/Supplementary-Table-3.xlsx
@@ -535,22 +535,22 @@
       </c>
       <c r="C2" s="5" t="inlineStr"/>
       <c r="D2" s="4" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E2" s="6" t="n">
-        <v>-66.41186736104038</v>
+        <v>-67.09777727386125</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>-68.68663238187065</v>
+        <v>-69.55614303915033</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>-7.005816458032588</v>
+        <v>-8.796058545034063</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>16.99900066419496</v>
+        <v>18.85121210583309</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>-7.718419185332086</v>
+        <v>-7.596787795509937</v>
       </c>
     </row>
     <row r="3">
@@ -564,22 +564,22 @@
       </c>
       <c r="C3" s="5" t="inlineStr"/>
       <c r="D3" s="4" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E3" s="6" t="n">
-        <v>-61.49999328430591</v>
+        <v>-66.63453948154265</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>-64.83560997899107</v>
+        <v>-69.1890813448113</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>-6.253771707739446</v>
+        <v>-8.72120501379259</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>17.27782494707272</v>
+        <v>18.90241416872801</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>-7.688436544648092</v>
+        <v>-7.626667291666764</v>
       </c>
     </row>
     <row r="4">
@@ -593,22 +593,22 @@
       </c>
       <c r="C4" s="5" t="inlineStr"/>
       <c r="D4" s="4" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>-66.16427425033113</v>
+        <v>-66.54819101102298</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>-68.25282248562766</v>
+        <v>-68.62206315097293</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>-9.040890960916244</v>
+        <v>-9.422941248495199</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>18.85339425125268</v>
+        <v>19.11685785873442</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>-7.723955055039881</v>
+        <v>-7.62004447028924</v>
       </c>
     </row>
     <row r="5">
@@ -624,22 +624,22 @@
         <v>1.1</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>-60.40815400796441</v>
+        <v>-63.18324857397994</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>-63.44334564664064</v>
+        <v>-66.02382924098322</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>-7.351850007577332</v>
+        <v>-8.564124362369444</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>18.07155203408994</v>
+        <v>18.94216094372605</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>-7.684510387836405</v>
+        <v>-7.537455914353321</v>
       </c>
     </row>
     <row r="6">
@@ -655,22 +655,22 @@
         <v>1.1</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>-61.76776035313105</v>
+        <v>-64.8607116214085</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>-65.41322837904237</v>
+        <v>-67.62716478586684</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>-6.539088162909104</v>
+        <v>-8.802448971576652</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>17.84675677465435</v>
+        <v>19.138141371324</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>-7.662200585833927</v>
+        <v>-7.56923923528901</v>
       </c>
     </row>
     <row r="7">
@@ -686,22 +686,22 @@
         <v>1.1</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>-64.58400657916043</v>
+        <v>-66.27582136462837</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>-67.66918259663913</v>
+        <v>-68.68031669547415</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>-7.180154835992631</v>
+        <v>-9.060258658889945</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>18.12584778546831</v>
+        <v>19.18362662167668</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>-7.860516931996973</v>
+        <v>-7.718872631940968</v>
       </c>
     </row>
     <row r="8">
@@ -717,22 +717,22 @@
         <v>1.2</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>-64.45114051904513</v>
+        <v>-67.70017615048951</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>-67.45540251103827</v>
+        <v>-69.75040323703979</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>-10.27039954078637</v>
+        <v>-11.31861515964937</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>21.00861719871798</v>
+        <v>21.0361664609745</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>-7.733955665938485</v>
+        <v>-7.667324214774838</v>
       </c>
     </row>
     <row r="9">
@@ -748,22 +748,22 @@
         <v>1.2</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>-65.25044366774296</v>
+        <v>-67.57488767861169</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>-67.648259263501</v>
+        <v>-69.89434702387092</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>-9.480856196237664</v>
+        <v>-11.21327683763739</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>19.65072045590636</v>
+        <v>21.20515270853134</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>-7.772048663910671</v>
+        <v>-7.672416525634707</v>
       </c>
     </row>
     <row r="10">
@@ -779,22 +779,22 @@
         <v>1.2</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>-65.792661442929</v>
+        <v>-67.2488877012722</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>-68.60718573345586</v>
+        <v>-69.51763444094004</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>-9.361331040638747</v>
+        <v>-10.69606493186452</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>19.9526052857904</v>
+        <v>20.62331869770874</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>-7.776749954624795</v>
+        <v>-7.658507026176379</v>
       </c>
     </row>
     <row r="11">
@@ -810,22 +810,22 @@
         <v>1.4</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>-62.95778207084517</v>
+        <v>-65.32770321982775</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>-66.36487946428976</v>
+        <v>-68.27940040187465</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>-7.813498958324842</v>
+        <v>-8.906081613771629</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>18.96053080804945</v>
+        <v>19.49714798316445</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>-7.739934456280039</v>
+        <v>-7.639369187345924</v>
       </c>
     </row>
     <row r="12">
@@ -841,22 +841,22 @@
         <v>1.4</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>-63.72598756336726</v>
+        <v>-65.37564845527885</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>-67.01210475757534</v>
+        <v>-67.8298437003639</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>-8.786756058091623</v>
+        <v>-9.461386505511172</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>19.74771164115482</v>
+        <v>19.49272026295415</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>-7.674838388855098</v>
+        <v>-7.577138512357927</v>
       </c>
     </row>
     <row r="13">
@@ -872,22 +872,22 @@
         <v>1.4</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>-61.96079965810659</v>
+        <v>-65.84541189571661</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>-65.35201240881888</v>
+        <v>-68.53128133300692</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>-8.034026906184669</v>
+        <v>-9.89535856456135</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>19.08418270643537</v>
+        <v>20.17639463763848</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>-7.658943049538432</v>
+        <v>-7.595166635786826</v>
       </c>
     </row>
     <row r="14">
@@ -903,22 +903,22 @@
         <v>2.7</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>-62.4624803430334</v>
+        <v>-65.61663932477923</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>-66.05485797771564</v>
+        <v>-68.45629387832098</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>-7.641005064456341</v>
+        <v>-8.95372622843791</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>18.92588275340502</v>
+        <v>19.37789410979524</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>-7.692500054266439</v>
+        <v>-7.584513327815564</v>
       </c>
     </row>
     <row r="15">
@@ -934,22 +934,22 @@
         <v>2.7</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>-62.61053655090234</v>
+        <v>-65.12259538430436</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>-65.70152832786376</v>
+        <v>-67.69013686663875</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>-6.272605387229088</v>
+        <v>-8.764351866906523</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>17.07663618127885</v>
+        <v>18.94447794379969</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>-7.713039017088327</v>
+        <v>-7.612584594558802</v>
       </c>
     </row>
     <row r="16">
@@ -965,22 +965,22 @@
         <v>2.7</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>-63.80051328473958</v>
+        <v>-64.83452668985116</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>-66.75195903615305</v>
+        <v>-67.17576673737389</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>-6.614831913019093</v>
+        <v>-8.190594067966973</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>17.34024083409209</v>
+        <v>18.13470179446568</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>-7.773963169659528</v>
+        <v>-7.602867678975968</v>
       </c>
     </row>
     <row r="17">
@@ -996,22 +996,22 @@
         <v>3.4</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>-60.75560140632334</v>
+        <v>-66.04991469817796</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>-64.55375301375172</v>
+        <v>-69.07355656661854</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>-7.134752521162296</v>
+        <v>-8.476784377480383</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>18.51566977528267</v>
+        <v>19.06576687245706</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>-7.582765646691988</v>
+        <v>-7.56534062653609</v>
       </c>
     </row>
     <row r="18">
@@ -1027,22 +1027,22 @@
         <v>3.4</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>-61.9343561463299</v>
+        <v>-64.46814623911486</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>-65.0136774373922</v>
+        <v>-67.81638702932558</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>-9.048143798403812</v>
+        <v>-9.040078094002419</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>19.90167866701378</v>
+        <v>19.97486131824909</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>-7.774213577547675</v>
+        <v>-7.586542434035934</v>
       </c>
     </row>
     <row r="19">
@@ -1058,22 +1058,22 @@
         <v>3.4</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>-61.64330800475344</v>
+        <v>-62.24962425088203</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>-65.19674052305882</v>
+        <v>-65.941716462158</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>-6.359447409131056</v>
+        <v>-7.872536201069202</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>17.57099227285294</v>
+        <v>19.09421752105479</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>-7.658112345416504</v>
+        <v>-7.529589108709623</v>
       </c>
     </row>
     <row r="20">
@@ -1089,22 +1089,22 @@
         <v>5.2</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>-59.76489069548006</v>
+        <v>-62.69269305063899</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>-64.82381835438861</v>
+        <v>-66.17054796113509</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>-5.433080729931698</v>
+        <v>-8.949906261293433</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>18.06768409152788</v>
+        <v>19.99145198734495</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>-7.57567570268766</v>
+        <v>-7.563690815555434</v>
       </c>
     </row>
     <row r="21">
@@ -1120,22 +1120,22 @@
         <v>5.2</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>-63.94669710583119</v>
+        <v>-66.01212816667055</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>-67.39882823002668</v>
+        <v>-68.99154222354659</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>-7.017787213456882</v>
+        <v>-8.998328801084355</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>18.19134661162104</v>
+        <v>19.61356762034487</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>-7.721428273968668</v>
+        <v>-7.635824762384476</v>
       </c>
     </row>
     <row r="22">
@@ -1151,22 +1151,22 @@
         <v>5.2</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>-60.13946200749179</v>
+        <v>-62.55163294836785</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>-64.30238051167346</v>
+        <v>-66.45581838380814</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>-5.391323535092177</v>
+        <v>-8.305346513185407</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>17.31593590621511</v>
+        <v>19.86631074325532</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>-7.761693866941259</v>
+        <v>-7.656778794629624</v>
       </c>
     </row>
     <row r="23">
@@ -1182,22 +1182,22 @@
         <v>6.8</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E23" s="6" t="n">
-        <v>-64.27584209331889</v>
+        <v>-65.75849507397595</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>-66.76002895873832</v>
+        <v>-68.59114156863215</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>-11.23395150476626</v>
+        <v>-11.12838587679184</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>21.52100630517672</v>
+        <v>21.59381355883742</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>-7.802867934991022</v>
+        <v>-7.632781187389366</v>
       </c>
     </row>
     <row r="24">
@@ -1213,22 +1213,22 @@
         <v>6.8</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E24" s="6" t="n">
-        <v>-67.09708682146669</v>
+        <v>-69.22046790936737</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>-68.85254065622728</v>
+        <v>-70.49654372824862</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>-11.02698025584098</v>
+        <v>-11.76090949184284</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>20.55442310428072</v>
+        <v>20.64339688813481</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>-7.771989013679168</v>
+        <v>-7.606411577410724</v>
       </c>
     </row>
     <row r="25">
@@ -1244,22 +1244,22 @@
         <v>6.8</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>-65.6315586982531</v>
+        <v>-67.06993400708348</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>-69.20409704793151</v>
+        <v>-69.95657140009465</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>-8.381723528574087</v>
+        <v>-9.520825404463729</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>19.7261222689831</v>
+        <v>20.06318361307877</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>-7.771860390730615</v>
+        <v>-7.655720815603865</v>
       </c>
     </row>
     <row r="26">
@@ -1275,22 +1275,22 @@
         <v>7.8</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E26" s="6" t="n">
-        <v>-62.28110152311058</v>
+        <v>-66.11675958383231</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>-65.49890916272631</v>
+        <v>-68.5800664023991</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>-8.617056242832012</v>
+        <v>-11.44890798576711</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>19.54350289149676</v>
+        <v>21.58077281018288</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>-7.708639009049016</v>
+        <v>-7.668558005848988</v>
       </c>
     </row>
     <row r="27">
@@ -1306,22 +1306,22 @@
         <v>7.8</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E27" s="6" t="n">
-        <v>-65.28186510769953</v>
+        <v>-66.56314457982262</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>-68.2650433521606</v>
+        <v>-68.99096631363946</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>-10.51925011851476</v>
+        <v>-11.70401371225826</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>21.29935456963387</v>
+        <v>21.78319768741527</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>-7.796926206658036</v>
+        <v>-7.651362241340184</v>
       </c>
     </row>
     <row r="28">
@@ -1337,22 +1337,22 @@
         <v>7.8</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>-63.66131155480423</v>
+        <v>-65.51164654573738</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>-67.7657268224678</v>
+        <v>-68.62801557173074</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>-6.453373468158327</v>
+        <v>-10.00774011364053</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>18.36398400038652</v>
+        <v>20.79306617977515</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>-7.806195264564645</v>
+        <v>-7.668957040141234</v>
       </c>
     </row>
     <row r="29">
@@ -1368,22 +1368,22 @@
         <v>18</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>-57.38008470734459</v>
+        <v>-64.35476105977115</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>-62.72151398173793</v>
+        <v>-68.32488048868106</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>-6.392180482656252</v>
+        <v>-9.500856413210409</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>19.52829046413502</v>
+        <v>21.25965999143757</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>-7.794680707085429</v>
+        <v>-7.788684149317258</v>
       </c>
     </row>
     <row r="30">
@@ -1399,22 +1399,22 @@
         <v>18</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E30" s="6" t="n">
-        <v>-55.53307693845253</v>
+        <v>-64.49514710743755</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>-59.54655137765724</v>
+        <v>-67.15165534405288</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>-7.127701082514587</v>
+        <v>-10.80424250733086</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>18.75110898829327</v>
+        <v>21.03105434724067</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>-7.609933466573974</v>
+        <v>-7.570303603294475</v>
       </c>
     </row>
     <row r="31">
@@ -1430,22 +1430,22 @@
         <v>18</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>-63.93414284051009</v>
+        <v>-65.61948241743548</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>-67.48864896870118</v>
+        <v>-69.2568189571799</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>-9.25581805838562</v>
+        <v>-10.75370691996366</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>20.60836943340119</v>
+        <v>22.09211337634756</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>-7.798045246824479</v>
+        <v>-7.701069916639455</v>
       </c>
     </row>
     <row r="32">
@@ -1461,22 +1461,22 @@
         <v>9.6</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>-61.22991977330631</v>
+        <v>-65.81739833036983</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>-64.26225314436225</v>
+        <v>-68.77800040194332</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>-8.857603995116015</v>
+        <v>-10.51244489405292</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>19.53291979620151</v>
+        <v>21.11306689209509</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>-7.642982430029553</v>
+        <v>-7.640019926468683</v>
       </c>
     </row>
     <row r="33">
@@ -1492,22 +1492,22 @@
         <v>9.6</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E33" s="6" t="n">
-        <v>-62.27982366724785</v>
+        <v>-64.85279784013534</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>-66.09613947758405</v>
+        <v>-68.27808134156015</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>-7.658326934147537</v>
+        <v>-7.898231477045996</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>19.1504311151304</v>
+        <v>18.89590006257562</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>-7.675788370646664</v>
+        <v>-7.572385084104812</v>
       </c>
     </row>
     <row r="34">
@@ -1523,22 +1523,22 @@
         <v>9.6</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>-62.1962470841568</v>
+        <v>-64.42025479212116</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>-65.6497284173828</v>
+        <v>-68.1202473158055</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>-8.129586442686289</v>
+        <v>-8.723291274832484</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>19.22535403964624</v>
+        <v>20.00690544084654</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>-7.64228626373393</v>
+        <v>-7.583621642329724</v>
       </c>
     </row>
     <row r="35">
@@ -1554,22 +1554,22 @@
         <v>11</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E35" s="6" t="n">
-        <v>-64.44003183381932</v>
+        <v>-65.34933151421892</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>-66.48651887073969</v>
+        <v>-67.64399836106071</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>-8.528535327745253</v>
+        <v>-10.10291752583729</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>18.38335480334426</v>
+        <v>20.0172792930676</v>
       </c>
       <c r="I35" s="6" t="n">
-        <v>-7.808332438678631</v>
+        <v>-7.619694920388508</v>
       </c>
     </row>
     <row r="36">
@@ -1585,22 +1585,22 @@
         <v>11</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E36" s="6" t="n">
-        <v>-61.40734173417953</v>
+        <v>-64.82348015710922</v>
       </c>
       <c r="F36" s="6" t="n">
-        <v>-64.53652688583327</v>
+        <v>-67.34949459643211</v>
       </c>
       <c r="G36" s="6" t="n">
-        <v>-8.700640827692087</v>
+        <v>-9.024705221186265</v>
       </c>
       <c r="H36" s="6" t="n">
-        <v>19.6601162904991</v>
+        <v>19.24850808502839</v>
       </c>
       <c r="I36" s="6" t="n">
-        <v>-7.830290311153258</v>
+        <v>-7.697788424519234</v>
       </c>
     </row>
     <row r="37">
@@ -1616,22 +1616,22 @@
         <v>11</v>
       </c>
       <c r="D37" s="4" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E37" s="6" t="n">
-        <v>-59.84600296582544</v>
+        <v>-65.50532151518961</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>-63.36437103676406</v>
+        <v>-68.16135663175464</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>-6.305163035204239</v>
+        <v>-8.859356987231893</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>17.52642573179752</v>
+        <v>19.16226839244252</v>
       </c>
       <c r="I37" s="6" t="n">
-        <v>-7.702894625654641</v>
+        <v>-7.646876288645581</v>
       </c>
     </row>
     <row r="38">
@@ -1647,22 +1647,22 @@
         <v>36</v>
       </c>
       <c r="D38" s="4" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E38" s="6" t="n">
-        <v>-66.30504766559341</v>
+        <v>-67.90934781691038</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>-68.38616329170409</v>
+        <v>-69.94081432524486</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>-11.37902648945127</v>
+        <v>-12.673219094893</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>21.28379540963109</v>
+        <v>22.38816920475568</v>
       </c>
       <c r="I38" s="6" t="n">
-        <v>-7.823653294069134</v>
+        <v>-7.68348360152819</v>
       </c>
     </row>
     <row r="39">
@@ -1678,22 +1678,22 @@
         <v>36</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E39" s="6" t="n">
-        <v>-63.43280365428983</v>
+        <v>-67.17745334906068</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>-65.80800289795776</v>
+        <v>-69.23032810360286</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>-8.913692429192212</v>
+        <v>-10.73894613992163</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>19.02037118178708</v>
+        <v>20.47230368590492</v>
       </c>
       <c r="I39" s="6" t="n">
-        <v>-7.731479508926945</v>
+        <v>-7.680482791441121</v>
       </c>
     </row>
     <row r="40">
@@ -1709,22 +1709,22 @@
         <v>36</v>
       </c>
       <c r="D40" s="4" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E40" s="6" t="n">
-        <v>-67.73235479061719</v>
+        <v>-69.45487799258538</v>
       </c>
       <c r="F40" s="6" t="n">
-        <v>-69.6635012781677</v>
+        <v>-71.04250211487761</v>
       </c>
       <c r="G40" s="6" t="n">
-        <v>-10.7515047550576</v>
+        <v>-11.7570753753683</v>
       </c>
       <c r="H40" s="6" t="n">
-        <v>20.44037783351045</v>
+        <v>21.00903830154448</v>
       </c>
       <c r="I40" s="6" t="n">
-        <v>-7.757726590902353</v>
+        <v>-7.664338803883947</v>
       </c>
     </row>
     <row r="41">
@@ -1740,22 +1740,22 @@
         <v>93</v>
       </c>
       <c r="D41" s="4" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E41" s="6" t="n">
-        <v>-61.90023933641923</v>
+        <v>-63.82111462913426</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>-64.80987174198351</v>
+        <v>-66.77364425108671</v>
       </c>
       <c r="G41" s="6" t="n">
-        <v>-7.994813228953026</v>
+        <v>-8.997072084813125</v>
       </c>
       <c r="H41" s="6" t="n">
-        <v>18.58446365560674</v>
+        <v>19.47158641158737</v>
       </c>
       <c r="I41" s="6" t="n">
-        <v>-7.680018021089396</v>
+        <v>-7.521984704821789</v>
       </c>
     </row>
     <row r="42">
@@ -1771,22 +1771,22 @@
         <v>93</v>
       </c>
       <c r="D42" s="4" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E42" s="6" t="n">
-        <v>-66.2657577285962</v>
+        <v>-64.57129879091609</v>
       </c>
       <c r="F42" s="6" t="n">
-        <v>-69.49180190846108</v>
+        <v>-67.56477246621237</v>
       </c>
       <c r="G42" s="6" t="n">
-        <v>-7.812051980914379</v>
+        <v>-8.780551588955026</v>
       </c>
       <c r="H42" s="6" t="n">
-        <v>18.75753585056867</v>
+        <v>19.33869854214086</v>
       </c>
       <c r="I42" s="6" t="n">
-        <v>-7.719439689789401</v>
+        <v>-7.564673277889565</v>
       </c>
     </row>
     <row r="43">
@@ -1802,22 +1802,22 @@
         <v>93</v>
       </c>
       <c r="D43" s="4" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E43" s="6" t="n">
-        <v>-62.63181740762563</v>
+        <v>-64.47872984530935</v>
       </c>
       <c r="F43" s="6" t="n">
-        <v>-65.41136114401274</v>
+        <v>-67.59546532473266</v>
       </c>
       <c r="G43" s="6" t="n">
-        <v>-7.962329169613958</v>
+        <v>-8.258982847035872</v>
       </c>
       <c r="H43" s="6" t="n">
-        <v>18.42533484471688</v>
+        <v>18.97811788445905</v>
       </c>
       <c r="I43" s="6" t="n">
-        <v>-7.6834619387158</v>
+        <v>-7.602399557999852</v>
       </c>
     </row>
     <row r="44">
@@ -1833,22 +1833,22 @@
         <v>105</v>
       </c>
       <c r="D44" s="4" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E44" s="6" t="n">
-        <v>-62.94888087946065</v>
+        <v>-64.78389758814367</v>
       </c>
       <c r="F44" s="6" t="n">
-        <v>-65.62317624511584</v>
+        <v>-67.03134999411152</v>
       </c>
       <c r="G44" s="6" t="n">
-        <v>-7.20673199916682</v>
+        <v>-8.972130138034352</v>
       </c>
       <c r="H44" s="6" t="n">
-        <v>17.57069035196395</v>
+        <v>18.80314480506211</v>
       </c>
       <c r="I44" s="6" t="n">
-        <v>-7.689662987141945</v>
+        <v>-7.583562261059908</v>
       </c>
     </row>
     <row r="45">
@@ -1864,22 +1864,22 @@
         <v>105</v>
       </c>
       <c r="D45" s="4" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E45" s="6" t="n">
-        <v>-61.40438469545907</v>
+        <v>-66.6308157636644</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>-65.2733120128117</v>
+        <v>-68.97920129867695</v>
       </c>
       <c r="G45" s="6" t="n">
-        <v>-7.409375493491372</v>
+        <v>-9.493116946378748</v>
       </c>
       <c r="H45" s="6" t="n">
-        <v>18.96220639376521</v>
+        <v>19.4461961913975</v>
       </c>
       <c r="I45" s="6" t="n">
-        <v>-7.683903582921219</v>
+        <v>-7.604693710006218</v>
       </c>
     </row>
     <row r="46">
@@ -1895,22 +1895,22 @@
         <v>105</v>
       </c>
       <c r="D46" s="4" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E46" s="6" t="n">
-        <v>-63.19230418506081</v>
+        <v>-65.89628285272188</v>
       </c>
       <c r="F46" s="6" t="n">
-        <v>-66.20473053403269</v>
+        <v>-68.22000597215091</v>
       </c>
       <c r="G46" s="6" t="n">
-        <v>-7.076692341409451</v>
+        <v>-8.611375335354554</v>
       </c>
       <c r="H46" s="6" t="n">
-        <v>17.82094716569889</v>
+        <v>18.56426507063623</v>
       </c>
       <c r="I46" s="6" t="n">
-        <v>-7.731828475317581</v>
+        <v>-7.629166615852662</v>
       </c>
     </row>
     <row r="47">
@@ -1926,22 +1926,22 @@
         <v>106</v>
       </c>
       <c r="D47" s="4" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E47" s="6" t="n">
-        <v>-63.35721956917848</v>
+        <v>-65.00963844142792</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>-67.67987633666645</v>
+        <v>-69.67403091029809</v>
       </c>
       <c r="G47" s="6" t="n">
-        <v>-6.095138710100167</v>
+        <v>-7.197022955622635</v>
       </c>
       <c r="H47" s="6" t="n">
-        <v>18.1542399736481</v>
+        <v>19.49667685346439</v>
       </c>
       <c r="I47" s="6" t="n">
-        <v>-7.736444496059964</v>
+        <v>-7.635261428971591</v>
       </c>
     </row>
     <row r="48">
@@ -1957,22 +1957,22 @@
         <v>106</v>
       </c>
       <c r="D48" s="4" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E48" s="6" t="n">
-        <v>-59.55520977055865</v>
+        <v>-62.99555030581424</v>
       </c>
       <c r="F48" s="6" t="n">
-        <v>-64.0270493709659</v>
+        <v>-66.57062987226591</v>
       </c>
       <c r="G48" s="6" t="n">
-        <v>-6.150344192954273</v>
+        <v>-8.879200776248497</v>
       </c>
       <c r="H48" s="6" t="n">
-        <v>18.26673082822139</v>
+        <v>20.0426537128981</v>
       </c>
       <c r="I48" s="6" t="n">
-        <v>-7.644547034859885</v>
+        <v>-7.588373370197944</v>
       </c>
     </row>
     <row r="49">
@@ -1988,22 +1988,22 @@
         <v>106</v>
       </c>
       <c r="D49" s="4" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E49" s="6" t="n">
-        <v>-63.72570167745989</v>
+        <v>-64.17700322708271</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>-68.2600395098287</v>
+        <v>-68.11181589841571</v>
       </c>
       <c r="G49" s="6" t="n">
-        <v>-7.34224626990441</v>
+        <v>-8.562452293753527</v>
       </c>
       <c r="H49" s="6" t="n">
-        <v>19.60760512269934</v>
+        <v>20.09331957559968</v>
       </c>
       <c r="I49" s="6" t="n">
-        <v>-7.73102102042612</v>
+        <v>-7.596054610513135</v>
       </c>
     </row>
     <row r="50">
@@ -2019,22 +2019,22 @@
         <v>149</v>
       </c>
       <c r="D50" s="4" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E50" s="6" t="n">
-        <v>-55.45246827565062</v>
+        <v>-64.09986954505132</v>
       </c>
       <c r="F50" s="6" t="n">
-        <v>-60.55706626460938</v>
+        <v>-67.18721287514228</v>
       </c>
       <c r="G50" s="6" t="n">
-        <v>-5.766204048843763</v>
+        <v>-8.332220419233321</v>
       </c>
       <c r="H50" s="6" t="n">
-        <v>18.55162776451038</v>
+        <v>19.04459008751134</v>
       </c>
       <c r="I50" s="6" t="n">
-        <v>-7.680825726707853</v>
+        <v>-7.625026338187047</v>
       </c>
     </row>
     <row r="51">
@@ -2050,22 +2050,22 @@
         <v>149</v>
       </c>
       <c r="D51" s="4" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E51" s="6" t="n">
-        <v>-60.8872567611179</v>
+        <v>-63.18961310303583</v>
       </c>
       <c r="F51" s="6" t="n">
-        <v>-64.69616904534712</v>
+        <v>-66.48846204107765</v>
       </c>
       <c r="G51" s="6" t="n">
-        <v>-6.247226210273294</v>
+        <v>-8.486998523432524</v>
       </c>
       <c r="H51" s="6" t="n">
-        <v>17.85157328581947</v>
+        <v>19.45240004340732</v>
       </c>
       <c r="I51" s="6" t="n">
-        <v>-7.795434791316948</v>
+        <v>-7.666552581932987</v>
       </c>
     </row>
     <row r="52">
@@ -2081,22 +2081,22 @@
         <v>149</v>
       </c>
       <c r="D52" s="4" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E52" s="6" t="n">
-        <v>-62.7668789994903</v>
+        <v>-64.64151632648895</v>
       </c>
       <c r="F52" s="6" t="n">
-        <v>-64.73279836068136</v>
+        <v>-66.94668297083321</v>
       </c>
       <c r="G52" s="6" t="n">
-        <v>-7.981150633842973</v>
+        <v>-9.178247113942756</v>
       </c>
       <c r="H52" s="6" t="n">
-        <v>17.71071732158186</v>
+        <v>19.1660612354315</v>
       </c>
       <c r="I52" s="6" t="n">
-        <v>-7.76364732654783</v>
+        <v>-7.682647477144493</v>
       </c>
     </row>
     <row r="53">
@@ -2112,22 +2112,22 @@
         <v>153</v>
       </c>
       <c r="D53" s="4" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E53" s="6" t="n">
-        <v>-62.16006825689269</v>
+        <v>-63.55126595214979</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>-66.85539957943936</v>
+        <v>-67.01531550068339</v>
       </c>
       <c r="G53" s="6" t="n">
-        <v>-4.879801745837087</v>
+        <v>-6.97887773176843</v>
       </c>
       <c r="H53" s="6" t="n">
-        <v>17.26802083775828</v>
+        <v>18.04666218292645</v>
       </c>
       <c r="I53" s="6" t="n">
-        <v>-7.69288776937452</v>
+        <v>-7.603734902624418</v>
       </c>
     </row>
     <row r="54">
@@ -2143,22 +2143,22 @@
         <v>153</v>
       </c>
       <c r="D54" s="4" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E54" s="6" t="n">
-        <v>-63.32545624788224</v>
+        <v>-66.22217767917377</v>
       </c>
       <c r="F54" s="6" t="n">
-        <v>-67.96568699806456</v>
+        <v>-70.43077248758739</v>
       </c>
       <c r="G54" s="6" t="n">
-        <v>-5.992840976913921</v>
+        <v>-8.12642106200342</v>
       </c>
       <c r="H54" s="6" t="n">
-        <v>18.48468744048197</v>
+        <v>19.9940199514648</v>
       </c>
       <c r="I54" s="6" t="n">
-        <v>-7.851615713385733</v>
+        <v>-7.659004081047743</v>
       </c>
     </row>
     <row r="55">
@@ -2174,22 +2174,22 @@
         <v>153</v>
       </c>
       <c r="D55" s="4" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E55" s="6" t="n">
-        <v>-65.12076076262976</v>
+        <v>-65.63288674488994</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>-69.33634336106626</v>
+        <v>-69.22376862527753</v>
       </c>
       <c r="G55" s="6" t="n">
-        <v>-10.03393573859443</v>
+        <v>-9.283871444365424</v>
       </c>
       <c r="H55" s="6" t="n">
-        <v>21.96725545376254</v>
+        <v>20.48082559560043</v>
       </c>
       <c r="I55" s="6" t="n">
-        <v>-7.717737116731603</v>
+        <v>-7.606072270847415</v>
       </c>
     </row>
     <row r="56">
@@ -2205,22 +2205,22 @@
         <v>161</v>
       </c>
       <c r="D56" s="4" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E56" s="6" t="n">
-        <v>-64.6850967772248</v>
+        <v>-63.96040883702542</v>
       </c>
       <c r="F56" s="6" t="n">
-        <v>-69.13721382001846</v>
+        <v>-67.51683470139947</v>
       </c>
       <c r="G56" s="6" t="n">
-        <v>-6.378324080191335</v>
+        <v>-8.08585015465485</v>
       </c>
       <c r="H56" s="6" t="n">
-        <v>18.60180220230131</v>
+        <v>19.19171880353705</v>
       </c>
       <c r="I56" s="6" t="n">
-        <v>-7.771361079316294</v>
+        <v>-7.549442784508145</v>
       </c>
     </row>
     <row r="57">
@@ -2236,22 +2236,22 @@
         <v>161</v>
       </c>
       <c r="D57" s="4" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E57" s="6" t="n">
-        <v>-63.05652470329457</v>
+        <v>-64.92406659240606</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>-67.13420568172613</v>
+        <v>-68.45964036484268</v>
       </c>
       <c r="G57" s="6" t="n">
-        <v>-7.336078162874113</v>
+        <v>-9.329239480590443</v>
       </c>
       <c r="H57" s="6" t="n">
-        <v>19.19969582420918</v>
+        <v>20.50222604726058</v>
       </c>
       <c r="I57" s="6" t="n">
-        <v>-7.785936682903515</v>
+        <v>-7.637412794233508</v>
       </c>
     </row>
     <row r="58">
@@ -2267,22 +2267,22 @@
         <v>161</v>
       </c>
       <c r="D58" s="4" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E58" s="6" t="n">
-        <v>-59.46617083640571</v>
+        <v>-64.29907857863724</v>
       </c>
       <c r="F58" s="6" t="n">
-        <v>-63.43835733377851</v>
+        <v>-69.03209850563611</v>
       </c>
       <c r="G58" s="6" t="n">
-        <v>-7.894189984677216</v>
+        <v>-8.101767218400594</v>
       </c>
       <c r="H58" s="6" t="n">
-        <v>19.64945588011586</v>
+        <v>20.48318566601318</v>
       </c>
       <c r="I58" s="6" t="n">
-        <v>-7.783079398065863</v>
+        <v>-7.64839852061372</v>
       </c>
     </row>
   </sheetData>

--- a/manuscript/post-feedback-from-atanu/Supplementary-Table-3.xlsx
+++ b/manuscript/post-feedback-from-atanu/Supplementary-Table-3.xlsx
@@ -3650,31 +3650,31 @@
         <v>1</v>
       </c>
       <c r="D32" s="7" t="n">
-        <v>-60.32</v>
+        <v>-56.26</v>
       </c>
       <c r="E32" s="7" t="n">
-        <v>-59.61</v>
+        <v>-55.69</v>
       </c>
       <c r="F32" s="7" t="n">
-        <v>-0.7100000000000009</v>
+        <v>-0.5700000000000003</v>
       </c>
       <c r="G32" s="7" t="n">
-        <v>-60.92</v>
+        <v>-57.35</v>
       </c>
       <c r="H32" s="7" t="n">
-        <v>-59.54</v>
+        <v>-54.75</v>
       </c>
       <c r="I32" s="7" t="n">
-        <v>-1.380000000000003</v>
+        <v>-2.600000000000001</v>
       </c>
       <c r="J32" s="7" t="n">
-        <v>-60.32</v>
+        <v>-56.26</v>
       </c>
       <c r="K32" s="7" t="n">
-        <v>-59.14</v>
+        <v>-55.73</v>
       </c>
       <c r="L32" s="7" t="n">
-        <v>-1.18</v>
+        <v>-0.5300000000000011</v>
       </c>
     </row>
     <row r="33">
@@ -3692,31 +3692,31 @@
         <v>2</v>
       </c>
       <c r="D33" s="7" t="n">
-        <v>-49.65</v>
+        <v>-46.34</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>-51.04</v>
+        <v>-50.58</v>
       </c>
       <c r="F33" s="7" t="n">
-        <v>1.390000000000001</v>
+        <v>4.239999999999995</v>
       </c>
       <c r="G33" s="7" t="n">
-        <v>-49.33</v>
+        <v>-47.94</v>
       </c>
       <c r="H33" s="7" t="n">
-        <v>-51.93</v>
+        <v>-51.71</v>
       </c>
       <c r="I33" s="7" t="n">
-        <v>2.600000000000001</v>
+        <v>3.770000000000003</v>
       </c>
       <c r="J33" s="7" t="n">
-        <v>-49.67</v>
+        <v>-45.14</v>
       </c>
       <c r="K33" s="7" t="n">
-        <v>-51.07</v>
+        <v>-50.57</v>
       </c>
       <c r="L33" s="7" t="n">
-        <v>1.399999999999999</v>
+        <v>5.43</v>
       </c>
     </row>
     <row r="34">
@@ -3734,31 +3734,31 @@
         <v>3</v>
       </c>
       <c r="D34" s="7" t="n">
-        <v>-47.69</v>
+        <v>-52.9</v>
       </c>
       <c r="E34" s="7" t="n">
-        <v>-53.01</v>
+        <v>-52.19</v>
       </c>
       <c r="F34" s="7" t="n">
-        <v>5.32</v>
+        <v>-0.7100000000000009</v>
       </c>
       <c r="G34" s="7" t="n">
-        <v>-48.62</v>
+        <v>-53.45</v>
       </c>
       <c r="H34" s="7" t="n">
-        <v>-55.08</v>
+        <v>-52.8</v>
       </c>
       <c r="I34" s="7" t="n">
-        <v>6.460000000000001</v>
+        <v>-0.6500000000000057</v>
       </c>
       <c r="J34" s="7" t="n">
-        <v>-47.94</v>
+        <v>-52.91</v>
       </c>
       <c r="K34" s="7" t="n">
-        <v>-53.01</v>
+        <v>-52.18</v>
       </c>
       <c r="L34" s="7" t="n">
-        <v>5.07</v>
+        <v>-0.7299999999999969</v>
       </c>
     </row>
     <row r="35">

--- a/manuscript/post-feedback-from-atanu/Supplementary-Table-3.xlsx
+++ b/manuscript/post-feedback-from-atanu/Supplementary-Table-3.xlsx
@@ -3692,31 +3692,31 @@
         <v>2</v>
       </c>
       <c r="D33" s="7" t="n">
-        <v>-46.34</v>
+        <v>-52.36</v>
       </c>
       <c r="E33" s="7" t="n">
         <v>-50.58</v>
       </c>
       <c r="F33" s="7" t="n">
-        <v>4.239999999999995</v>
+        <v>-1.780000000000001</v>
       </c>
       <c r="G33" s="7" t="n">
-        <v>-47.94</v>
+        <v>-53.86</v>
       </c>
       <c r="H33" s="7" t="n">
         <v>-51.71</v>
       </c>
       <c r="I33" s="7" t="n">
-        <v>3.770000000000003</v>
+        <v>-2.149999999999999</v>
       </c>
       <c r="J33" s="7" t="n">
-        <v>-45.14</v>
+        <v>-52.36</v>
       </c>
       <c r="K33" s="7" t="n">
         <v>-50.57</v>
       </c>
       <c r="L33" s="7" t="n">
-        <v>5.43</v>
+        <v>-1.789999999999999</v>
       </c>
     </row>
     <row r="34">
